--- a/viewer/data/lc_book_groupings.xlsx
+++ b/viewer/data/lc_book_groupings.xlsx
@@ -2,87 +2,71 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chipp\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\chipp\OneDrive\Documents\fanyahanwen-corpus\viewer\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8D5D6D-FC93-4659-8934-E211115A25AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE0AB098-B03D-40FA-8C47-7CFD4ABCEE5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36060" yWindow="1365" windowWidth="19590" windowHeight="11925" xr2:uid="{4CAA9252-EBAA-485F-B0D6-26EAA66BF78E}"/>
+    <workbookView xWindow="4830" yWindow="2805" windowWidth="19590" windowHeight="11925" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="187">
   <si>
     <t>Numbered Cultural Term</t>
   </si>
   <si>
+    <t>English</t>
+  </si>
+  <si>
     <t>Texts</t>
   </si>
   <si>
-    <t>English</t>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Synonyms</t>
   </si>
   <si>
     <t>五經</t>
   </si>
   <si>
+    <t>Five Classics</t>
+  </si>
+  <si>
+    <t>詩經，尚書，易經，禮記，春秋</t>
+  </si>
+  <si>
     <t>四書</t>
   </si>
   <si>
+    <t>Four Books</t>
+  </si>
+  <si>
+    <t>大學，中庸，論語，孟子</t>
+  </si>
+  <si>
+    <t>大學 and 中庸 are technically 禮記 chapters, so this is a bit anachronistic.</t>
+  </si>
+  <si>
     <t>十三經</t>
   </si>
   <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>Five Classics</t>
-  </si>
-  <si>
-    <t>Four Books</t>
-  </si>
-  <si>
-    <t>詩經，尚書，易經，禮記，春秋</t>
-  </si>
-  <si>
     <t>Thirteen Confucian Classics</t>
   </si>
   <si>
     <t>周易，尚書，詩經，周禮，儀禮，禮記，春秋左傳，春秋公羊傳，春秋穀梁傳，論語，孝經，爾雅，孟子</t>
   </si>
   <si>
-    <t>大學，中庸，論語，孟子</t>
-  </si>
-  <si>
-    <t>大學 and 中庸 are technically 禮記 chapters, so this is a bit anachronistic.</t>
-  </si>
-  <si>
     <t>六經</t>
   </si>
   <si>
@@ -95,9 +79,6 @@
     <t>樂經 is not extant</t>
   </si>
   <si>
-    <t>Synonyms</t>
-  </si>
-  <si>
     <t>六藝</t>
   </si>
   <si>
@@ -131,6 +112,9 @@
     <t>三百千</t>
   </si>
   <si>
+    <t>Sanbaiqian</t>
+  </si>
+  <si>
     <t>三字經，百家姓，千字文</t>
   </si>
   <si>
@@ -149,18 +133,30 @@
     <t>Twenty-Four Histories</t>
   </si>
   <si>
+    <t>史記，漢書，後漢書，三國志，晉書，宋書，南齊書，梁書，陳書，魏書，北齊書，周書，隋書，南史，北史，舊唐書，新唐書，舊五代史，新五代史，宋史，遼史，金史，元史，明史</t>
+  </si>
+  <si>
     <t>三倉</t>
   </si>
   <si>
+    <t>San Cang</t>
+  </si>
+  <si>
+    <t>倉頡篇，爰歷篇，博學篇</t>
+  </si>
+  <si>
+    <t>Only 倉頡篇 seems extant</t>
+  </si>
+  <si>
     <t>三禮</t>
   </si>
   <si>
+    <t>Three Ritual Classics</t>
+  </si>
+  <si>
     <t>周禮，禮記，儀禮</t>
   </si>
   <si>
-    <t>Three Ritual Classics</t>
-  </si>
-  <si>
     <t>前四史</t>
   </si>
   <si>
@@ -173,55 +169,418 @@
     <t>六国史</t>
   </si>
   <si>
+    <t>Japan's Six Histories</t>
+  </si>
+  <si>
     <t>日本書紀，続日本紀，日本後紀，続日本後紀，日本文徳天皇実録，日本三代実録</t>
   </si>
   <si>
     <t>勅撰三集</t>
   </si>
   <si>
+    <t>Japan's Three Anthologies</t>
+  </si>
+  <si>
     <t>凌雲集，文華秀麗集，経国集</t>
   </si>
   <si>
     <t>三代格式</t>
   </si>
   <si>
+    <t>Japan's Three Law Books</t>
+  </si>
+  <si>
     <t>弘仁格式，貞観格式，延喜格式</t>
   </si>
   <si>
     <t>三經</t>
   </si>
   <si>
+    <t>Korea's Three Classics</t>
+  </si>
+  <si>
     <t>詩經，尚書，易經</t>
   </si>
   <si>
     <t>Korean grouping for 五經四書</t>
   </si>
   <si>
-    <t>史記，漢書，後漢書，三國志，晉書，宋書，南齊書，梁書，陳書，魏書，北齊書，周書，隋書，南史，北史，舊唐書，新唐書，舊五代史，新五代史，宋史，遼史，金史，元史，明史</t>
-  </si>
-  <si>
-    <t>San Cang</t>
-  </si>
-  <si>
-    <t>倉頡篇，爰歷篇，博學篇</t>
-  </si>
-  <si>
-    <t>Sanbaiqian</t>
-  </si>
-  <si>
-    <t>Only 倉頡篇 seems extant</t>
-  </si>
-  <si>
-    <t>Japan's Six Histories</t>
-  </si>
-  <si>
-    <t>Korea's Three Classics</t>
-  </si>
-  <si>
-    <t>Japan's Three Anthologies</t>
-  </si>
-  <si>
-    <t>Japan's Three Law Books</t>
+    <t>Eighteen Indian Non-Buddhist Classics</t>
+  </si>
+  <si>
+    <t>荷力皮陀，冶受皮陀，三摩皮陀，阿闥皮陀，式叉論，毘伽羅論，柯刺波論，竪底沙論，闡陀論，尼鹿多論，肩亡婆論，那邪毘薩多論，伊底呵婆論，僧佉論，課伽論，陀菟論，楗闡婆論，阿輸論</t>
+  </si>
+  <si>
+    <t>In Jizang 吉藏's 百論疏: 四皮陀 + 六論 + 八論.</t>
+  </si>
+  <si>
+    <t>四皮陀</t>
+  </si>
+  <si>
+    <t>Four Vedas</t>
+  </si>
+  <si>
+    <t>荷力皮陀，冶受皮陀，三摩皮陀，阿闥皮陀</t>
+  </si>
+  <si>
+    <t>One of the three subdivisions of 十八大經 in Jizang 吉藏's 百論疏.</t>
+  </si>
+  <si>
+    <t>四韋陀</t>
+  </si>
+  <si>
+    <t>六論</t>
+  </si>
+  <si>
+    <t>Six Treatises</t>
+  </si>
+  <si>
+    <t>式叉論，毘伽羅論，柯刺波論，竪底沙論，闡陀論，尼鹿多論</t>
+  </si>
+  <si>
+    <t>八論</t>
+  </si>
+  <si>
+    <t>Eight Treatises</t>
+  </si>
+  <si>
+    <t>肩亡婆論，那邪毘薩多論，伊底呵婆論，僧佉論，課伽論，陀菟論，楗闡婆論，阿輸論</t>
+  </si>
+  <si>
+    <t>七經</t>
+  </si>
+  <si>
+    <t>Seven Classics</t>
+  </si>
+  <si>
+    <t>詩經，尚書，周易，儀禮，春秋，論語，孝經</t>
+  </si>
+  <si>
+    <t>七典</t>
+  </si>
+  <si>
+    <t>九經</t>
+  </si>
+  <si>
+    <t>Nine Classics</t>
+  </si>
+  <si>
+    <t>周易，尚書，毛詩，周禮，儀禮，禮記，春秋左傳，春秋公羊傳，春秋穀梁傳</t>
+  </si>
+  <si>
+    <t>十二經</t>
+  </si>
+  <si>
+    <t>Twelve Classics</t>
+  </si>
+  <si>
+    <t>周易，尚書，毛詩，周禮，儀禮，禮記，春秋左傳，春秋公羊傳，春秋穀梁傳，孝經，論語，爾雅</t>
+  </si>
+  <si>
+    <t>The twelve classics of the 開成石經, completed in 837.</t>
+  </si>
+  <si>
+    <t>十史</t>
+  </si>
+  <si>
+    <t>Ten Histories</t>
+  </si>
+  <si>
+    <t>三國志，晉書，宋書，南齊書，梁書，陳書，魏書，北齊書，周書，隋書</t>
+  </si>
+  <si>
+    <t>Tang grouping of dynastic histories from the Three Kingdoms through Sui.</t>
+  </si>
+  <si>
+    <t>十三史</t>
+  </si>
+  <si>
+    <t>Thirteen Histories</t>
+  </si>
+  <si>
+    <t>史記，漢書，後漢書，三國志，晉書，宋書，南齊書，梁書，陳書，魏書，北齊書，周書，隋書</t>
+  </si>
+  <si>
+    <t>Tang grouping: 史記、漢書、後漢書 + 十史.</t>
+  </si>
+  <si>
+    <t>十三代史</t>
+  </si>
+  <si>
+    <t>十七史</t>
+  </si>
+  <si>
+    <t>Seventeen Histories</t>
+  </si>
+  <si>
+    <t>史記，漢書，後漢書，三國志，晉書，宋書，南齊書，梁書，陳書，魏書，北齊書，周書，隋書，南史，北史，新唐書，新五代史</t>
+  </si>
+  <si>
+    <t>Song-period grouping.</t>
+  </si>
+  <si>
+    <t>十八史</t>
+  </si>
+  <si>
+    <t>Eighteen Histories</t>
+  </si>
+  <si>
+    <t>史記，漢書，後漢書，三國志，晉書，宋書，南齊書，梁書，陳書，魏書，北齊書，周書，隋書，南史，北史，新唐書，新五代史，宋代史事</t>
+  </si>
+  <si>
+    <t>As reflected in Zeng, Xianzhi 曾先之's 十八史略: the 十七史 corpus plus a Song section drawing on later chronicles, before the official 宋史.</t>
+  </si>
+  <si>
+    <t>二十一史</t>
+  </si>
+  <si>
+    <t>Twenty-One Histories</t>
+  </si>
+  <si>
+    <t>史記，漢書，後漢書，三國志，晉書，宋書，南齊書，梁書，陳書，魏書，北齊書，周書，隋書，南史，北史，新唐書，新五代史，宋史，遼史，金史，元史</t>
+  </si>
+  <si>
+    <t>Ming-period grouping.</t>
+  </si>
+  <si>
+    <t>二十二史</t>
+  </si>
+  <si>
+    <t>Twenty-Two Histories</t>
+  </si>
+  <si>
+    <t>史記，漢書，後漢書，三國志，晉書，宋書，南齊書，梁書，陳書，魏書，北齊書，周書，隋書，南史，北史，新唐書，新五代史，宋史，遼史，金史，元史，明史</t>
+  </si>
+  <si>
+    <t>Early-Qing grouping after the completion of 明史.</t>
+  </si>
+  <si>
+    <t>二十三史</t>
+  </si>
+  <si>
+    <t>Twenty-Three Histories</t>
+  </si>
+  <si>
+    <t>史記，漢書，後漢書，三國志，晉書，宋書，南齊書，梁書，陳書，魏書，北齊書，周書，隋書，南史，北史，舊唐書，新唐書，新五代史，宋史，遼史，金史，元史，明史</t>
+  </si>
+  <si>
+    <t>Qing transitional grouping after 舊唐書 was added; 舊五代史 was later restored to form 二十四史.</t>
+  </si>
+  <si>
+    <t>三玄</t>
+  </si>
+  <si>
+    <t>Three Mysteries</t>
+  </si>
+  <si>
+    <t>老子，莊子，周易</t>
+  </si>
+  <si>
+    <t>Established medieval grouping.</t>
+  </si>
+  <si>
+    <t>四子真經</t>
+  </si>
+  <si>
+    <t>Four Daoist True Scriptures</t>
+  </si>
+  <si>
+    <t>南華真經，通玄真經，沖虛真經，洞靈真經</t>
+  </si>
+  <si>
+    <t>Established from Tang imperial canonization of works associated with 莊子、文子、列子、亢倉子; title forms vary in early records.</t>
+  </si>
+  <si>
+    <t>道教五大經典</t>
+  </si>
+  <si>
+    <t>Five Great Daoist Classics</t>
+  </si>
+  <si>
+    <t>陰符經，道德經，南華經，文始真經，黃庭經</t>
+  </si>
+  <si>
+    <t>Modern collective term attested in Huang, Gongwei 黃公偉 (1979).</t>
+  </si>
+  <si>
+    <t>三通</t>
+  </si>
+  <si>
+    <t>Three Comprehensive Histories</t>
+  </si>
+  <si>
+    <t>通典，通志，文獻通考</t>
+  </si>
+  <si>
+    <t>Traditional grouping of major institutional histories.</t>
+  </si>
+  <si>
+    <t>三論</t>
+  </si>
+  <si>
+    <t>Three Treatises</t>
+  </si>
+  <si>
+    <t>中論，百論，十二門論</t>
+  </si>
+  <si>
+    <t>East Asian Buddhist grouping.</t>
+  </si>
+  <si>
+    <t>四論</t>
+  </si>
+  <si>
+    <t>Four Treatises</t>
+  </si>
+  <si>
+    <t>中論，百論，十二門論，大智度論</t>
+  </si>
+  <si>
+    <t>四阿含</t>
+  </si>
+  <si>
+    <t>Four Āgamas</t>
+  </si>
+  <si>
+    <t>長阿含經，中阿含經，雜阿含經，增一阿含經</t>
+  </si>
+  <si>
+    <t>Standard East Asian Buddhist grouping.</t>
+  </si>
+  <si>
+    <t>天台三大部</t>
+  </si>
+  <si>
+    <t>Tiantai Three Great Works</t>
+  </si>
+  <si>
+    <t>法華玄義，法華文句，摩訶止觀</t>
+  </si>
+  <si>
+    <t>Works taught by Zhiyi 智顗 and recorded or edited by Guanding 灌頂.</t>
+  </si>
+  <si>
+    <t>法華三大部</t>
+  </si>
+  <si>
+    <t>三経義疏</t>
+  </si>
+  <si>
+    <t>Japan's Three Sutra Commentaries</t>
+  </si>
+  <si>
+    <t>勝鬘経義疏，維摩経義疏，法華義疏</t>
+  </si>
+  <si>
+    <t>Traditionally attributed to Shōtoku Taishi 聖徳太子; authorship is disputed.</t>
+  </si>
+  <si>
+    <t>浄土三部経</t>
+  </si>
+  <si>
+    <t>Three Pure Land Sutras</t>
+  </si>
+  <si>
+    <t>無量寿経，観無量寿経，阿弥陀経</t>
+  </si>
+  <si>
+    <t>Japanese Buddhist grouping; named as a set by Hōnen 法然.</t>
+  </si>
+  <si>
+    <t>法華三部経</t>
+  </si>
+  <si>
+    <t>Threefold Lotus Sutra</t>
+  </si>
+  <si>
+    <t>無量義経，妙法蓮華経，観普賢菩薩行法経</t>
+  </si>
+  <si>
+    <t>Japanese and East Asian Buddhist grouping.</t>
+  </si>
+  <si>
+    <t>護国三部経</t>
+  </si>
+  <si>
+    <t>Three Nation-Protecting Sutras</t>
+  </si>
+  <si>
+    <t>法華経，仁王経，金光明経</t>
+  </si>
+  <si>
+    <t>Japanese Buddhist grouping.</t>
+  </si>
+  <si>
+    <t>鎮護国家三部経</t>
+  </si>
+  <si>
+    <t>真言三部経</t>
+  </si>
+  <si>
+    <t>Three Shingon Sutras</t>
+  </si>
+  <si>
+    <t>大日経，金剛頂経，蘇悉地経</t>
+  </si>
+  <si>
+    <t>Japanese Shingon Buddhist grouping.</t>
+  </si>
+  <si>
+    <t>大日三部経，三部の秘経</t>
+  </si>
+  <si>
+    <t>四書三經</t>
+  </si>
+  <si>
+    <t>Korea's Four Books and Three Classics</t>
+  </si>
+  <si>
+    <t>大學，中庸，論語，孟子，詩經，尚書，易經</t>
+  </si>
+  <si>
+    <t>Joseon-period curricular and examination grouping.</t>
+  </si>
+  <si>
+    <t>三大全</t>
+  </si>
+  <si>
+    <t>Three Great Compendia</t>
+  </si>
+  <si>
+    <t>四書大全，五經大全，性理大全</t>
+  </si>
+  <si>
+    <t>Ming Yongle compilations; transmitted to Korea and Vietnam in the early fifteenth century.</t>
+  </si>
+  <si>
+    <t>永樂三大全</t>
+  </si>
+  <si>
+    <t>琉球三大史書</t>
+  </si>
+  <si>
+    <t>Ryukyu's Three Great Histories</t>
+  </si>
+  <si>
+    <t>中山世鑑，中山世譜，球陽</t>
+  </si>
+  <si>
+    <t>Modern scholarly and publishing collective term. 中山世鑑 is principally Japanese-language, with Han material.</t>
+  </si>
+  <si>
+    <t>三大官修史書</t>
+  </si>
+  <si>
+    <t>大越史記全書，欽定越史通鑑綱目，大南實錄</t>
+  </si>
+  <si>
+    <t>Modern scholarly collective term for three extant Vietnamese court-compiled histories.</t>
+  </si>
+  <si>
+    <t>Vietnam's Three Official Histories</t>
+  </si>
+  <si>
+    <t>Used in Tang examination curricula</t>
   </si>
 </sst>
 </file>
@@ -233,8 +592,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -319,108 +676,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -432,23 +695,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="67000"/>
                 <a:lumMod val="110000"/>
                 <a:satMod val="105000"/>
-                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:tint val="73000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="103000"/>
-                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="81000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="109000"/>
-                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -458,23 +721,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
                 <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:shade val="100000"/>
+                <a:lumMod val="100000"/>
                 <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:shade val="78000"/>
                 <a:lumMod val="99000"/>
                 <a:satMod val="120000"/>
-                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -482,26 +745,23 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -536,17 +796,17 @@
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -561,42 +821,19 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD019B6B-82E5-404A-8349-EED4483CEF90}">
-  <dimension ref="A1:E18"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.7109375" customWidth="1"/>
+    <col min="2" max="2" width="32.42578125" customWidth="1"/>
+    <col min="4" max="4" width="106.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -604,66 +841,66 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
       <c r="D1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
         <v>7</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E5" t="s">
         <v>19</v>
@@ -673,6 +910,15 @@
       <c r="A6" t="s">
         <v>20</v>
       </c>
+      <c r="B6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" t="s">
+        <v>63</v>
+      </c>
       <c r="E6" t="s">
         <v>21</v>
       </c>
@@ -707,115 +953,553 @@
         <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B12" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C14" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B15" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C15" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B16" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C16" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B17" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C17" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="B18" t="s">
         <v>58</v>
       </c>
       <c r="C18" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="D18" t="s">
-        <v>51</v>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19" t="s">
+        <v>67</v>
+      </c>
+      <c r="E19" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" t="s">
+        <v>70</v>
+      </c>
+      <c r="C20" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" t="s">
+        <v>73</v>
+      </c>
+      <c r="C21" t="s">
+        <v>74</v>
+      </c>
+      <c r="D21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" t="s">
+        <v>77</v>
+      </c>
+      <c r="E22" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>79</v>
+      </c>
+      <c r="B23" t="s">
+        <v>80</v>
+      </c>
+      <c r="C23" t="s">
+        <v>81</v>
+      </c>
+      <c r="D23" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B24" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" t="s">
+        <v>84</v>
+      </c>
+      <c r="D24" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>86</v>
+      </c>
+      <c r="B25" t="s">
+        <v>87</v>
+      </c>
+      <c r="C25" t="s">
+        <v>88</v>
+      </c>
+      <c r="D25" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>90</v>
+      </c>
+      <c r="B26" t="s">
+        <v>91</v>
+      </c>
+      <c r="C26" t="s">
+        <v>92</v>
+      </c>
+      <c r="D26" t="s">
+        <v>93</v>
+      </c>
+      <c r="E26" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>95</v>
+      </c>
+      <c r="B27" t="s">
+        <v>96</v>
+      </c>
+      <c r="C27" t="s">
+        <v>97</v>
+      </c>
+      <c r="D27" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>99</v>
+      </c>
+      <c r="B28" t="s">
+        <v>100</v>
+      </c>
+      <c r="C28" t="s">
+        <v>101</v>
+      </c>
+      <c r="D28" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>103</v>
+      </c>
+      <c r="B29" t="s">
+        <v>104</v>
+      </c>
+      <c r="C29" t="s">
+        <v>105</v>
+      </c>
+      <c r="D29" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>107</v>
+      </c>
+      <c r="B30" t="s">
+        <v>108</v>
+      </c>
+      <c r="C30" t="s">
+        <v>109</v>
+      </c>
+      <c r="D30" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>111</v>
+      </c>
+      <c r="B31" t="s">
+        <v>112</v>
+      </c>
+      <c r="C31" t="s">
+        <v>113</v>
+      </c>
+      <c r="D31" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>115</v>
+      </c>
+      <c r="B32" t="s">
+        <v>116</v>
+      </c>
+      <c r="C32" t="s">
+        <v>117</v>
+      </c>
+      <c r="D32" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>119</v>
+      </c>
+      <c r="B33" t="s">
+        <v>120</v>
+      </c>
+      <c r="C33" t="s">
+        <v>121</v>
+      </c>
+      <c r="D33" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>123</v>
+      </c>
+      <c r="B34" t="s">
+        <v>124</v>
+      </c>
+      <c r="C34" t="s">
+        <v>125</v>
+      </c>
+      <c r="D34" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>127</v>
+      </c>
+      <c r="B35" t="s">
+        <v>128</v>
+      </c>
+      <c r="C35" t="s">
+        <v>129</v>
+      </c>
+      <c r="D35" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>131</v>
+      </c>
+      <c r="B36" t="s">
+        <v>132</v>
+      </c>
+      <c r="C36" t="s">
+        <v>133</v>
+      </c>
+      <c r="D36" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>135</v>
+      </c>
+      <c r="B37" t="s">
+        <v>136</v>
+      </c>
+      <c r="C37" t="s">
+        <v>137</v>
+      </c>
+      <c r="D37" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>138</v>
+      </c>
+      <c r="B38" t="s">
+        <v>139</v>
+      </c>
+      <c r="C38" t="s">
+        <v>140</v>
+      </c>
+      <c r="D38" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>142</v>
+      </c>
+      <c r="B39" t="s">
+        <v>143</v>
+      </c>
+      <c r="C39" t="s">
+        <v>144</v>
+      </c>
+      <c r="D39" t="s">
+        <v>145</v>
+      </c>
+      <c r="E39" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>147</v>
+      </c>
+      <c r="B40" t="s">
+        <v>148</v>
+      </c>
+      <c r="C40" t="s">
+        <v>149</v>
+      </c>
+      <c r="D40" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>151</v>
+      </c>
+      <c r="B41" t="s">
+        <v>152</v>
+      </c>
+      <c r="C41" t="s">
+        <v>153</v>
+      </c>
+      <c r="D41" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>155</v>
+      </c>
+      <c r="B42" t="s">
+        <v>156</v>
+      </c>
+      <c r="C42" t="s">
+        <v>157</v>
+      </c>
+      <c r="D42" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>159</v>
+      </c>
+      <c r="B43" t="s">
+        <v>160</v>
+      </c>
+      <c r="C43" t="s">
+        <v>161</v>
+      </c>
+      <c r="D43" t="s">
+        <v>162</v>
+      </c>
+      <c r="E43" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>164</v>
+      </c>
+      <c r="B44" t="s">
+        <v>165</v>
+      </c>
+      <c r="C44" t="s">
+        <v>166</v>
+      </c>
+      <c r="D44" t="s">
+        <v>167</v>
+      </c>
+      <c r="E44" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>169</v>
+      </c>
+      <c r="B45" t="s">
+        <v>170</v>
+      </c>
+      <c r="C45" t="s">
+        <v>171</v>
+      </c>
+      <c r="D45" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>173</v>
+      </c>
+      <c r="B46" t="s">
+        <v>174</v>
+      </c>
+      <c r="C46" t="s">
+        <v>175</v>
+      </c>
+      <c r="D46" t="s">
+        <v>176</v>
+      </c>
+      <c r="E46" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>178</v>
+      </c>
+      <c r="B47" t="s">
+        <v>179</v>
+      </c>
+      <c r="C47" t="s">
+        <v>180</v>
+      </c>
+      <c r="D47" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>182</v>
+      </c>
+      <c r="B48" t="s">
+        <v>185</v>
+      </c>
+      <c r="C48" t="s">
+        <v>183</v>
+      </c>
+      <c r="D48" t="s">
+        <v>184</v>
       </c>
     </row>
   </sheetData>
